--- a/starter_kits/KIT-MFG-NONFERROUS-PROCUREMENT/1.0.0/templates/excel/MDM-07.xlsx
+++ b/starter_kits/KIT-MFG-NONFERROUS-PROCUREMENT/1.0.0/templates/excel/MDM-07.xlsx
@@ -16,7 +16,7 @@
     <sheet name="CHECKS" sheetId="6" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">DATA!$A$1:$T$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">DATA!$A$1:$S$5</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -51,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="146">
   <si>
     <r>
       <rPr>
@@ -317,17 +317,37 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">tenant_id·scope_node_id·cost_center_name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">이 없으면 </t>
+      <t xml:space="preserve">tenant_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">와 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">scope_node_id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF111827"/>
+        <rFont val="맑은 고딕"/>
+        <family val="2"/>
+        <charset val="129"/>
+      </rPr>
+      <t xml:space="preserve">가 없으면 </t>
     </r>
     <r>
       <rPr>
@@ -558,9 +578,6 @@
     <t xml:space="preserve">cost_center_id</t>
   </si>
   <si>
-    <t xml:space="preserve">cost_center_name</t>
-  </si>
-  <si>
     <t xml:space="preserve">pnl_line</t>
   </si>
   <si>
@@ -615,9 +632,6 @@
     <t xml:space="preserve">CC-PROC</t>
   </si>
   <si>
-    <t xml:space="preserve">원료구매 원가센터</t>
-  </si>
-  <si>
     <t xml:space="preserve">BALANCE_SHEET</t>
   </si>
   <si>
@@ -648,9 +662,6 @@
     <t xml:space="preserve">CC-LOG</t>
   </si>
   <si>
-    <t xml:space="preserve">물류 원가센터</t>
-  </si>
-  <si>
     <t xml:space="preserve">mdm-07-fe7447aaab41</t>
   </si>
   <si>
@@ -669,9 +680,6 @@
     <t xml:space="preserve">CC-MFG</t>
   </si>
   <si>
-    <t xml:space="preserve">생산 원가센터</t>
-  </si>
-  <si>
     <t xml:space="preserve">필드명</t>
   </si>
   <si>
@@ -1681,7 +1689,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">cost_center_name</t>
+      <t xml:space="preserve">pnl_line</t>
     </r>
   </si>
   <si>
@@ -1743,7 +1751,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">pnl_line</t>
+      <t xml:space="preserve">cashflow_line</t>
     </r>
   </si>
   <si>
@@ -1805,8 +1813,11 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">cashflow_line</t>
-    </r>
+      <t xml:space="preserve">currency</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean</t>
   </si>
   <si>
     <r>
@@ -1867,71 +1878,6 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">currency</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">계정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">원가요소</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">원가센터의 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
       <t xml:space="preserve">active</t>
     </r>
   </si>
@@ -2439,64 +2385,6 @@
     <t xml:space="preserve">MDM·Crosswalk</t>
   </si>
   <si>
-    <t xml:space="preserve">VAL-07</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">같은 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">cost_center_id</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">의 명칭</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·tenant·scope</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">가 모두 일치</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">원가센터 집합 정본</t>
-  </si>
-  <si>
     <t xml:space="preserve">지표</t>
   </si>
   <si>
@@ -2581,36 +2469,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">필수 범위</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF111827"/>
-        <rFont val="맑은 고딕"/>
-        <family val="2"/>
-        <charset val="129"/>
-      </rPr>
-      <t xml:space="preserve">원가센터 명칭 누락</t>
-    </r>
+    <t xml:space="preserve">범위 누락</t>
   </si>
   <si>
     <r>
@@ -2966,9 +2825,9 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_MDM_07" displayName="T_MDM_07" ref="A1:T5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <autoFilter ref="A1:T5"/>
-  <tableColumns count="20">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="T_MDM_07" displayName="T_MDM_07" ref="A1:S5" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <autoFilter ref="A1:S5"/>
+  <tableColumns count="19">
     <tableColumn id="1" name="record_id"/>
     <tableColumn id="2" name="tenant_id"/>
     <tableColumn id="3" name="scope_node_id"/>
@@ -2984,11 +2843,10 @@
     <tableColumn id="13" name="account_type"/>
     <tableColumn id="14" name="cost_element"/>
     <tableColumn id="15" name="cost_center_id"/>
-    <tableColumn id="16" name="cost_center_name"/>
-    <tableColumn id="17" name="pnl_line"/>
-    <tableColumn id="18" name="cashflow_line"/>
-    <tableColumn id="19" name="currency"/>
-    <tableColumn id="20" name="active"/>
+    <tableColumn id="16" name="pnl_line"/>
+    <tableColumn id="17" name="cashflow_line"/>
+    <tableColumn id="18" name="currency"/>
+    <tableColumn id="19" name="active"/>
   </tableColumns>
 </table>
 </file>
@@ -3333,7 +3191,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:T5"/>
+  <dimension ref="A1:S5"/>
   <sheetFormatPr defaultColWidth="7.65625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="19.27"/>
@@ -3349,9 +3207,8 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.01"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="12" style="0" width="12.84"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14.68"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="16.51"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="17" style="0" width="13.76"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="20" min="19" style="0" width="11.01"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="16" style="0" width="13.76"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="18" style="0" width="11.01"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3412,194 +3269,182 @@
       <c r="S1" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="T1" s="6" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="2" customFormat="false" ht="28.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="C2" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="E2" s="7" t="s">
         <v>42</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="F2" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F2" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="H2" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H2" s="7" t="s">
+      <c r="I2" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="J2" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="J2" s="7" t="s">
+      <c r="K2" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="K2" s="7" t="s">
+      <c r="L2" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L2" s="8" t="s">
+      <c r="M2" s="7" t="s">
         <v>49</v>
       </c>
-      <c r="M2" s="7" t="s">
+      <c r="N2" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="N2" s="7" t="s">
+      <c r="O2" s="7" t="s">
         <v>51</v>
       </c>
-      <c r="O2" s="7" t="s">
+      <c r="P2" s="7" t="s">
         <v>52</v>
       </c>
-      <c r="P2" s="8" t="s">
+      <c r="Q2" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="Q2" s="7" t="s">
+      <c r="R2" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R2" s="7" t="s">
+      <c r="S2" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="S2" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="K3" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H3" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J3" s="7" t="s">
+      <c r="L3" s="8" t="s">
         <v>59</v>
       </c>
-      <c r="K3" s="7" t="s">
+      <c r="M3" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N3" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="L3" s="8" t="s">
+      <c r="O3" s="7" t="s">
         <v>61</v>
       </c>
-      <c r="M3" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N3" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="O3" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="P3" s="8" t="s">
-        <v>64</v>
+      <c r="P3" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="Q3" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R3" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R3" s="7" t="s">
+      <c r="S3" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="S3" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="24.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="7" t="s">
+        <v>41</v>
+      </c>
+      <c r="G4" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="H4" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="I4" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="J4" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="K4" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="L4" s="8" t="s">
         <v>65</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>40</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>41</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>42</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="H4" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>46</v>
-      </c>
-      <c r="J4" s="7" t="s">
+      <c r="M4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="N4" s="7" t="s">
         <v>66</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="O4" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L4" s="8" t="s">
-        <v>68</v>
-      </c>
-      <c r="M4" s="7" t="s">
-        <v>50</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>70</v>
-      </c>
-      <c r="P4" s="8" t="s">
-        <v>71</v>
+      <c r="P4" s="7" t="s">
+        <v>52</v>
       </c>
       <c r="Q4" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="R4" s="7" t="s">
         <v>54</v>
       </c>
-      <c r="R4" s="7" t="s">
+      <c r="S4" s="7" t="s">
         <v>55</v>
-      </c>
-      <c r="S4" s="7" t="s">
-        <v>56</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3622,10 +3467,9 @@
       <c r="Q5" s="9"/>
       <c r="R5" s="9"/>
       <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:T5"/>
+  <autoFilter ref="A1:S5"/>
   <dataValidations count="4">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D2:D1005" type="list">
       <formula1>"ACTUAL,PLAN,FORECAST,SCENARIO,REFERENCE,SYNTHETIC"</formula1>
@@ -3664,7 +3508,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="7.65625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.69"/>
@@ -3676,19 +3520,19 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D1" s="10" t="s">
         <v>11</v>
       </c>
       <c r="E1" s="10" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3696,16 +3540,16 @@
         <v>19</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D2" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3713,16 +3557,16 @@
         <v>20</v>
       </c>
       <c r="B3" s="11" t="s">
+        <v>72</v>
+      </c>
+      <c r="C3" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D3" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>76</v>
-      </c>
-      <c r="C3" s="11" t="s">
-        <v>77</v>
-      </c>
-      <c r="D3" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>80</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3730,16 +3574,16 @@
         <v>21</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C4" s="11" t="s">
+        <v>73</v>
+      </c>
+      <c r="D4" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="D4" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3747,16 +3591,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D5" s="11" t="s">
+        <v>74</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>78</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3764,16 +3608,16 @@
         <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3781,16 +3625,16 @@
         <v>24</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3798,16 +3642,16 @@
         <v>25</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D8" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3815,16 +3659,16 @@
         <v>26</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D9" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3832,16 +3676,16 @@
         <v>27</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D10" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3849,16 +3693,16 @@
         <v>28</v>
       </c>
       <c r="B11" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C11" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D11" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3866,16 +3710,16 @@
         <v>29</v>
       </c>
       <c r="B12" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3883,16 +3727,16 @@
         <v>30</v>
       </c>
       <c r="B13" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D13" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3900,16 +3744,16 @@
         <v>31</v>
       </c>
       <c r="B14" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C14" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D14" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3917,16 +3761,16 @@
         <v>32</v>
       </c>
       <c r="B15" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C15" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D15" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3934,16 +3778,16 @@
         <v>33</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3951,16 +3795,16 @@
         <v>34</v>
       </c>
       <c r="B17" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D17" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3968,16 +3812,16 @@
         <v>35</v>
       </c>
       <c r="B18" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C18" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D18" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -3985,16 +3829,16 @@
         <v>36</v>
       </c>
       <c r="B19" s="11" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C19" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D19" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4002,33 +3846,16 @@
         <v>37</v>
       </c>
       <c r="B20" s="11" t="s">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="11" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="11" t="s">
-        <v>98</v>
-      </c>
-      <c r="C21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="D21" s="11" t="s">
-        <v>78</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -4056,13 +3883,13 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4070,10 +3897,10 @@
         <v>22</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4081,10 +3908,10 @@
         <v>23</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4092,10 +3919,10 @@
         <v>23</v>
       </c>
       <c r="B4" s="11" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4103,10 +3930,10 @@
         <v>23</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4114,10 +3941,10 @@
         <v>23</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4125,10 +3952,10 @@
         <v>23</v>
       </c>
       <c r="B7" s="11" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4136,10 +3963,10 @@
         <v>25</v>
       </c>
       <c r="B8" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4147,10 +3974,10 @@
         <v>25</v>
       </c>
       <c r="B9" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -4158,10 +3985,10 @@
         <v>26</v>
       </c>
       <c r="B10" s="11" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -4180,7 +4007,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D7"/>
   <sheetFormatPr defaultColWidth="7.65625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="12.84"/>
@@ -4191,55 +4018,55 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>119</v>
+        <v>114</v>
       </c>
       <c r="D1" s="10" t="s">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="11" t="s">
-        <v>121</v>
+        <v>116</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>122</v>
+        <v>117</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>124</v>
+        <v>119</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>125</v>
+        <v>120</v>
       </c>
       <c r="B3" s="11" t="s">
-        <v>126</v>
+        <v>121</v>
       </c>
       <c r="C3" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D3" s="11" t="s">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="11" t="s">
-        <v>128</v>
+        <v>123</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D4" s="11" t="s">
         <v>12</v>
@@ -4247,13 +4074,13 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>131</v>
+        <v>126</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D5" s="11" t="s">
         <v>14</v>
@@ -4261,44 +4088,30 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="11" t="s">
-        <v>132</v>
+        <v>127</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>133</v>
+        <v>128</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>123</v>
+        <v>118</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>134</v>
+        <v>129</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>135</v>
+        <v>130</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>114</v>
+        <v>109</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="11" t="s">
-        <v>138</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C8" s="11" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
     </row>
   </sheetData>
@@ -4327,73 +4140,73 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="10" t="s">
-        <v>141</v>
+        <v>133</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>143</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="B2" s="12" t="n">
         <f aca="false">COUNTA(DATA!A:A)-1</f>
         <v>3</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>145</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="11" t="s">
-        <v>146</v>
+        <v>138</v>
       </c>
       <c r="B3" s="12" t="n">
         <f aca="false">COUNTIF(DATA!D:D,"SYNTHETIC")</f>
         <v>3</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>147</v>
+        <v>139</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>148</v>
+        <v>140</v>
       </c>
       <c r="B4" s="12" t="str">
         <f aca="false">IF(B2=B3,"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="B5" s="12" t="n">
-        <f aca="false">COUNTBLANK(DATA!C2:INDEX(DATA!C:C,B2+1))+COUNTBLANK(DATA!P2:INDEX(DATA!P:P,B2+1))</f>
+        <f aca="false">COUNTBLANK(DATA!C2:INDEX(DATA!C:C,B2+1))</f>
         <v>0</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="B6" s="12" t="str">
         <f aca="false">IF(AND(B4="PASS",B5=0),"PASS","REVIEW")</f>
         <v>PASS</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
     </row>
   </sheetData>
